--- a/Data/mauryaEmpire.xlsx
+++ b/Data/mauryaEmpire.xlsx
@@ -472,119 +472,119 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Where was the Third Buddhist Council held?</t>
+          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Vishnu Gupta</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
+          <t>Who built the first stone Buddhist monuments in India?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rock Edict II</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Minor Edict I</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
+          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Max Müller</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>War strategies</t>
+          <t>Alexander Cunningham</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Territorial expansion</t>
+          <t>William Jones</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>144</v>
+        <v>58</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
+          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -604,7 +604,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -616,5252 +616,5252 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>92</v>
+        <v>148</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who was appointed to promote Dhamma among women?</t>
+          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yuvrajas</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Rajukas</t>
+          <t>Ambassadors</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sanghamitras</t>
+          <t>NGOs</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What was the key feature of Mauryan pillars?</t>
+          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Red granite</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Sanskrit carvings</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gold-plated tops</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>115</v>
+        <v>79</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>What was the purpose of Ashoka’s rock edicts?</t>
+          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Religious conversion</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Personal glorification</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Historical record</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>45</v>
+        <v>84</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known for religious tolerance?</t>
+          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a Mauryan ruler?</t>
+          <t>Who among the following was not sent as a missionary by Ashoka?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Rakkhita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>68</v>
+        <v>59</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>What administrative division existed under Maurya rule?</t>
+          <t>Who succeeded Ashoka as emperor?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Janapadas</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Mahajanapadas</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Districts</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>96</v>
+        <v>147</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The Maurya Empire began in which year (approx)?</t>
+          <t>Which officer was responsible for maintaining law and order?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>273 BCE</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>200 BCE</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12</v>
+        <v>135</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
+          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Chinese traveler praised the Mauryan governance?</t>
+          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Xuanzang</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Dasharatha</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>15</v>
+        <v>95</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What was the profession of Chanakya before becoming a political advisor?</t>
+          <t>Which area was not fully controlled by the Mauryas?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>Deccan</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Trader</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Kashmir</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
+          <t>Which city did Ashoka develop into a major Buddhist center?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Bodh Gaya</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Kushinagar</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>116</v>
+        <v>57</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
+          <t>What was the role of 'Antapala' in Mauryan administration?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Chief priest</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Finance minister</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>82</v>
+        <v>150</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
+          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Devavarman</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Brihadratha</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109</v>
+        <v>7</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which Buddhist council did Ashoka support?</t>
+          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>How many provinces were there during Ashoka’s reign?</t>
+          <t>What was the primary language of Ashoka’s southern edicts?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136</v>
+        <v>121</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
+          <t>The Kalinga war took place around which year?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>100 BCE</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>133</v>
+        <v>75</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>What does the name "Ashoka" literally mean?</t>
+          <t>The Lion Capital of Ashoka has how many lions?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Without enemies</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>One who shines</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Protector of Dharma</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>37</v>
+        <v>107</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
+          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Responsible for judiciary</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Minister of religion</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Advisor to Emperor</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
+          <t>Which of these rivers was near the capital of the Mauryas?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>102</v>
+        <v>61</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who was the son of Chandragupta Maurya?</t>
+          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict II</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Minor Edict I</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
+          <t>What was Ashoka’s religion before converting to Buddhism?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Animism</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Ajivika</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>38</v>
+        <v>15</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>The term 'Samaharta' in Mauryan administration meant:</t>
+          <t>What was the profession of Chanakya before becoming a political advisor?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Army general</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Spiritual leader</t>
+          <t>Trader</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>11</v>
+        <v>64</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What is the name of the script used in Ashoka's inscriptions?</t>
+          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Treaty of Magadha</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Treaty of Taxila</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Treaty of Indus</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>104</v>
+        <v>140</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Which title did Ashoka use for himself in inscriptions?</t>
+          <t>The Mauryan army was primarily composed of which units?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Samrat</t>
+          <t>Infantry</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Elephants</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maharajadhiraja</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Ashokan inscription at Girnar is in which modern state?</t>
+          <t>Who was Ashoka's chief queen?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya?</t>
+          <t>Where did Megasthenes reside as a Greek ambassador?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>77</v>
+        <v>133</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
+          <t>What does the name "Ashoka" literally mean?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Without enemies</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>One who shines</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Economic reforms</t>
+          <t>Protector of Dharma</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>145</v>
+        <v>83</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which term referred to a municipal officer under the Mauryas?</t>
+          <t>Which modern Indian state was part of ancient Kalinga?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mahamattas</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>53</v>
+        <v>138</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What was the main source of revenue in Mauryan administration?</t>
+          <t>The Ashokan inscription at Girnar is in which modern state?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1</v>
+        <v>108</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who was the founder of the Maurya Empire?</t>
+          <t>What was the name of the spy network in Mauryan administration?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Sanstha</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chaturanga</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vyayam</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129</v>
+        <v>109</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
+          <t>Which Buddhist council did Ashoka support?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Victory rituals</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Coronation rituals</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Marriage festivals</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was the head monk at the Third Buddhist Council?</t>
+          <t>Who was appointed to promote Dhamma among women?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Yuvrajas</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Ananda</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kassapa</t>
+          <t>Rajukas</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Sanghamitras</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>101</v>
+        <v>88</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which city served as the capital of the Maurya Empire?</t>
+          <t>What was the rank of a provincial governor in Mauryan administration?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Mahamatra</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Which system did Mauryans follow for currency?</t>
+          <t>What was the purpose of Ashoka’s rock edicts?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Cowry-based</t>
+          <t>Religious conversion</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Gold coins</t>
+          <t>Personal glorification</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Silver coins</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Historical record</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>88</v>
+        <v>10</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What was the rank of a provincial governor in Mauryan administration?</t>
+          <t>Which of the following was NOT a Mauryan ruler?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mahamatra</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>55</v>
+        <v>5</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
+          <t>What book did Megasthenes write?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Natya Shastra</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>70</v>
+        <v>16</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
+          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Mehrauli</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Delhi-Topra</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>89</v>
+        <v>11</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>The Ashokan edicts were mainly meant to:</t>
+          <t>What is the name of the script used in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Promote taxation</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Record wars</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Praise deities</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
+          <t>Which ancient text is believed to describe the Mauryan administration?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Treaty of Magadha</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Treaty of Taxila</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Treaty of Indus</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>71</v>
+        <v>117</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
+          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which area was not fully controlled by the Mauryas?</t>
+          <t>How many provinces were there during Ashoka’s reign?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Deccan</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kashmir</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123</v>
+        <v>39</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
+          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashoka’s title "Devanampiya" means:</t>
+          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Son of Buddha</t>
+          <t>Respect for elders</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Conqueror of Kalinga</t>
+          <t>Religious tolerance</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lord of Kings</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>139</v>
+        <v>112</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
+          <t>The Lion Capital of Ashoka is now the emblem of:</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>111</v>
+        <v>23</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
+          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
       <c r="E50" t="inlineStr">
         <is>
+          <t>Chandragupta Maurya</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
           <t>Dasharatha</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>Kaniska</t>
-        </is>
-      </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
+          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Ashvaghosha</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>141</v>
+        <v>26</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
+          <t>Which southern kingdom did Ashoka not conquer?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Forts</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Trade routes</t>
+          <t>Pandya</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Chera</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Who was Ashoka's chief queen?</t>
+          <t>Which science was advanced under Mauryan rule?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Metallurgy</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
+          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Sudharma</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>46</v>
+        <v>12</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
+          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>First Council</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Second Council</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fourth Council</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>97</v>
+        <v>1</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
+          <t>Who was the founder of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mauryan glaze</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Ashokan polish</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mirror carving</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
+          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ashvaghosha</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is located at:</t>
+          <t>Who succeeded Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>57</v>
+        <v>9</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>What was the role of 'Antapala' in Mauryan administration?</t>
+          <t>Which religion did Ashoka promote after the Kalinga War?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Chief priest</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Finance minister</t>
+          <t>Zoroastrianism</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
+          <t>The Ashokan edicts were mainly meant to:</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Promote taxation</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Record wars</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Became a republic</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Shifted capital</t>
+          <t>Praise deities</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
+          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Persians</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Egyptians</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>103</v>
+        <v>31</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
+          <t>What was the name of the tax collected during the Mauryan rule?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Shunga</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Sharada</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2</v>
+        <v>96</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
+          <t>The Maurya Empire began in which year (approx)?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>273 BCE</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Vishnu Gupta</t>
+          <t>200 BCE</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>84</v>
+        <v>111</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
+          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Kaniska</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>106</v>
+        <v>145</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
+          <t>Which term referred to a municipal officer under the Mauryas?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Mahamattas</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
+          <t>The term 'Samaharta' in Mauryan administration meant:</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Army general</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Spiritual leader</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>4</v>
+        <v>116</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
+          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Pliny</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Seleucus</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>33</v>
+        <v>124</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which ancient text is believed to describe the Mauryan administration?</t>
+          <t>Which natural element was used to polish Mauryan pillars?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Quartz</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Which science was advanced under Mauryan rule?</t>
+          <t>What was the name of the currency used during the Maurya period?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Rupya</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Niska</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Metallurgy</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>36</v>
+        <v>127</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which of these rivers was near the capital of the Mauryas?</t>
+          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>War strategies</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Territorial expansion</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ashoka sent missionaries to which of the following regions?</t>
+          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Arabia</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tibet</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka has how many lions?</t>
+          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Became a republic</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Shifted capital</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which of the following was a major port during Mauryan rule?</t>
+          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>First Council</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Bharuch</t>
+          <t>Second Council</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Kaveripattinam</t>
+          <t>Fourth Council</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Which religion did Ashoka promote after the Kalinga War?</t>
+          <t>After which war did Ashoka convert to Buddhism?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Taxila Revolt</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Zoroastrianism</t>
+          <t>Battle of Magadha</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>142</v>
+        <v>17</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who built the first stone Buddhist monuments in India?</t>
+          <t>Which Ashokan edict mentions the Kalinga War?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Minor Pillar Edict I</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Harsha</t>
+          <t>Pillar Edict VII</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>56</v>
+        <v>97</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Mauryan king followed Jainism in his later life?</t>
+          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Mauryan glaze</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ashokan polish</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Mirror carving</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>13</v>
+        <v>128</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
+          <t>Which edict talks about religious tolerance by Ashoka?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Minor Rock Edict I</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Pillar Edict III</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rock Edict VI</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>41</v>
+        <v>114</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which city did Ashoka develop into a major Buddhist center?</t>
+          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Bodh Gaya</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kushinagar</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>110</v>
+        <v>4</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Sanchi Stupa was originally commissioned by:</t>
+          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Pliny</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Seleucus</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>137</v>
+        <v>48</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who compiled the Arthashastra?</t>
+          <t>Who was the head monk at the Third Buddhist Council?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Ananda</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Kassapa</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128</v>
+        <v>45</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which edict talks about religious tolerance by Ashoka?</t>
+          <t>Which Mauryan ruler was known for religious tolerance?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Minor Rock Edict I</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Pillar Edict III</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rock Edict VI</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112</v>
+        <v>13</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is now the emblem of:</t>
+          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>31</v>
+        <v>137</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>What was the name of the tax collected during the Mauryan rule?</t>
+          <t>Who compiled the Arthashastra?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Sharada</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
+          <t>What material were most of the Ashokan pillars made from?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Granite</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Sandalwood</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Minor Rock Edict</t>
+          <t>Marble</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>26</v>
+        <v>146</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which southern kingdom did Ashoka not conquer?</t>
+          <t>What was the status of women under Mauryan rule?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Highly suppressed</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Equal to men</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Pandya</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Chera</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
+          <t>In which language were Ashoka’s inscriptions mostly written?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>93</v>
+        <v>35</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler gave up violence completely?</t>
+          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
+          <t>Which profession was part of state control under Mauryan rule?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Medical practice</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>140</v>
+        <v>119</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Mauryan army was primarily composed of which units?</t>
+          <t>Which Chinese traveler praised the Mauryan governance?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Infantry</t>
+          <t>Xuanzang</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Elephants</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>All of the above</t>
-        </is>
-      </c>
+          <t>Megasthenes</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
+          <t>What administrative division existed under Maurya rule?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Janapadas</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Mahajanapadas</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Districts</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134</v>
+        <v>71</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
+          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Persian</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>21</v>
+        <v>144</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
+          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What was the primary language of Ashoka’s southern edicts?</t>
+          <t>Which of the following was a major port during Mauryan rule?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Bharuch</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Kaveripattinam</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
+          <t>What was the official language of Mauryan administration?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which of the following was a key feature of Mauryan administration?</t>
+          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Feudal system</t>
+          <t>Bactria</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Tribal governance</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Decentralized rule</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>131</v>
+        <v>105</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Who were the Sthanikas in the Mauryan system?</t>
+          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Village guards</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Persian king</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Army commanders</t>
+          <t>Roman emperor</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Egyptian Pharaoh</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>81</v>
+        <v>27</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
+          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Bactria</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>122</v>
+        <v>24</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Which king was known as “Ashoka the Great”?</t>
+          <t>Where did Chandragupta Maurya spend his last years?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Where did Megasthenes reside as a Greek ambassador?</t>
+          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>90</v>
+        <v>3</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
+          <t>What was the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Persians</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Egyptians</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>16</v>
+        <v>82</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
+          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mehrauli</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Delhi-Topra</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124</v>
+        <v>53</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which natural element was used to polish Mauryan pillars?</t>
+          <t>What was the main source of revenue in Mauryan administration?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Quartz</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>148</v>
+        <v>94</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
+          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Ambassadors</t>
+          <t>Western India</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>NGOs</t>
+          <t>Coastal India</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
+          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>29</v>
+        <v>87</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Ashoka’s policy after the Kalinga war was called?</t>
+          <t>Which profession was supervised during Mauryan times for quality control?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Rajadharma</t>
+          <t>Carpenters</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Ahimsa</t>
+          <t>Doctors</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Blacksmiths</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sangha</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>135</v>
+        <v>40</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
+          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Sudharma</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>83</v>
+        <v>131</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which modern Indian state was part of ancient Kalinga?</t>
+          <t>Who were the Sthanikas in the Mauryan system?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Village guards</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Army commanders</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>50</v>
+        <v>101</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
+          <t>Which city served as the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Expansion of navy</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Increase in cavalry</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Recruitment from Kalinga</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Who succeeded Ashoka as emperor?</t>
+          <t>Which Mauryan ruler gave up violence completely?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
           <t>Dasharatha</t>
         </is>
       </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>Kunala</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>20</v>
+        <v>102</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
+          <t>Who was the son of Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which officer was responsible for maintaining law and order?</t>
+          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>War</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Victory</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126</v>
+        <v>49</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which branch of philosophy did Chanakya support?</t>
+          <t>Ashoka’s title "Devanampiya" means:</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Son of Buddha</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Vedanta</t>
+          <t>Conqueror of Kalinga</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Lord of Kings</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>32</v>
+        <v>77</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
+          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Economic reforms</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>143</v>
+        <v>70</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which son of Ashoka ruled the western part of the empire?</t>
+          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Sumana</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>149</v>
+        <v>129</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>The Mauryan period marked the beginning of what type of administration?</t>
+          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Victory rituals</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Feudalism</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Coronation rituals</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Guild-based</t>
+          <t>Marriage festivals</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>94</v>
+        <v>139</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
+          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Western India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Coastal India</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
+          <t>The Sanchi Stupa was originally commissioned by:</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Alexander Cunningham</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>William Jones</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>What was the status of women under Mauryan rule?</t>
+          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Highly suppressed</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Equal to men</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which dynasty succeeded the Maurya Empire?</t>
+          <t>The Lion Capital of Ashoka is located at:</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
+          <t>The Maurya Empire was established in which century BCE?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Ibn Battuta</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Marco Polo</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>125</v>
+        <v>37</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor ruled the longest?</t>
+          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Responsible for judiciary</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Minister of religion</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Advisor to Emperor</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
+          <t>Ashoka sent missionaries to which of the following regions?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Arabia</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Tibet</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>35</v>
+        <v>122</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
+          <t>Which king was known as “Ashoka the Great”?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>27</v>
+        <v>126</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
+          <t>Which branch of philosophy did Chanakya support?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>3</v>
+        <v>103</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>What was the capital of the Maurya Empire?</t>
+          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Shunga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
+          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Rock Edict III</t>
+          <t>Indica</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Mahabhashya</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Where did Chandragupta Maurya spend his last years?</t>
+          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>After which war did Ashoka convert to Buddhism?</t>
+          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Taxila Revolt</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Battle of Magadha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>17</v>
+        <v>104</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which Ashokan edict mentions the Kalinga War?</t>
+          <t>Which title did Ashoka use for himself in inscriptions?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Samrat</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Minor Pillar Edict I</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Pillar Edict VII</t>
+          <t>Maharajadhiraja</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>99</v>
+        <v>60</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
+          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
+          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Expansion of navy</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Increase in cavalry</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Recruitment from Kalinga</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>114</v>
+        <v>28</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
+          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121</v>
+        <v>149</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The Kalinga war took place around which year?</t>
+          <t>The Mauryan period marked the beginning of what type of administration?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Feudalism</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>100 BCE</t>
+          <t>Guild-based</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>98</v>
+        <v>19</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which site has a monolithic Ashokan elephant statue?</t>
+          <t>What was the main focus of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Military expansion</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Religious conversions</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Rampurva</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Kumhrar</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>54</v>
+        <v>29</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>The Maurya Empire was established in which century BCE?</t>
+          <t>Ashoka’s policy after the Kalinga war was called?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Rajadharma</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Ahimsa</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Sangha</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>108</v>
+        <v>56</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>What was the name of the spy network in Mauryan administration?</t>
+          <t>Which Mauryan king followed Jainism in his later life?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Sanstha</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chaturanga</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Vyayam</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>150</v>
+        <v>47</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
+          <t>Where was the Third Buddhist Council held?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Devavarman</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Brihadratha</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Who among the following was not sent as a missionary by Ashoka?</t>
+          <t>Which of the following was a key feature of Mauryan administration?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Feudal system</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Tribal governance</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Rakkhita</t>
+          <t>Decentralized rule</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>117</v>
+        <v>98</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
+          <t>Which site has a monolithic Ashokan elephant statue?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Rampurva</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Kumhrar</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>What material were most of the Ashokan pillars made from?</t>
+          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Granite</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Sandalwood</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Marble</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>What was the name of the currency used during the Maurya period?</t>
+          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Rupya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Niska</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>What was the official language of Mauryan administration?</t>
+          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Rock Edict III</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>19</v>
+        <v>132</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>What was the main focus of Ashoka’s Dhamma?</t>
+          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Military expansion</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Religious conversions</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Minor Rock Edict</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>5</v>
+        <v>141</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>What book did Megasthenes write?</t>
+          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Forts</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Trade routes</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Natya Shastra</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>91</v>
+        <v>143</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
+          <t>Which son of Ashoka ruled the western part of the empire?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Respect for elders</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Religious tolerance</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Sumana</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>130</v>
+        <v>43</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Which profession was part of state control under Mauryan rule?</t>
+          <t>What was the key feature of Mauryan pillars?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Red granite</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Sanskrit carvings</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Medical practice</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Gold-plated tops</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>What was Ashoka’s religion before converting to Buddhism?</t>
+          <t>Which system did Mauryans follow for currency?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Cowry-based</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Animism</t>
+          <t>Gold coins</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Silver coins</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ajivika</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
+          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Persian king</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Roman emperor</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Egyptian Pharaoh</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>87</v>
+        <v>14</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which profession was supervised during Mauryan times for quality control?</t>
+          <t>Which dynasty succeeded the Maurya Empire?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Doctors</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Blacksmiths</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>In which language were Ashoka’s inscriptions mostly written?</t>
+          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Ibn Battuta</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Marco Polo</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>76</v>
+        <v>125</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
+          <t>Which Mauryan emperor ruled the longest?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Indica</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mahabhashya</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>

--- a/Data/mauryaEmpire.xlsx
+++ b/Data/mauryaEmpire.xlsx
@@ -472,1919 +472,1915 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>2</v>
+        <v>119</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
+          <t>Which Chinese traveler praised the Mauryan governance?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Xuanzang</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Chanakya</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Vishnu Gupta</t>
-        </is>
-      </c>
+          <t>Megasthenes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>142</v>
+        <v>71</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Who built the first stone Buddhist monuments in India?</t>
+          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Persian</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harsha</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120</v>
+        <v>30</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
+          <t>Which of the following was a key feature of Mauryan administration?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Feudal system</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Alexander Cunningham</t>
+          <t>Tribal governance</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>William Jones</t>
+          <t>Decentralized rule</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
+          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>148</v>
+        <v>44</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
+          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ambassadors</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>NGOs</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
+          <t>What was the primary language of Ashoka’s southern edicts?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79</v>
+        <v>14</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
+          <t>Which dynasty succeeded the Maurya Empire?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>84</v>
+        <v>57</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
+          <t>What was the role of 'Antapala' in Mauryan administration?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Chief priest</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Finance minister</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who among the following was not sent as a missionary by Ashoka?</t>
+          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Responsible for judiciary</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Minister of religion</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rakkhita</t>
+          <t>Advisor to Emperor</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>59</v>
+        <v>93</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Who succeeded Ashoka as emperor?</t>
+          <t>Which Mauryan ruler gave up violence completely?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
           <t>Dasharatha</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Kunala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>147</v>
+        <v>39</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which officer was responsible for maintaining law and order?</t>
+          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135</v>
+        <v>41</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
+          <t>Which city did Ashoka develop into a major Buddhist center?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Bodh Gaya</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Kushinagar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134</v>
+        <v>3</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
+          <t>What was the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>95</v>
+        <v>81</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which area was not fully controlled by the Mauryas?</t>
+          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Deccan</t>
+          <t>Bactria</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kashmir</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>41</v>
+        <v>96</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Which city did Ashoka develop into a major Buddhist center?</t>
+          <t>The Maurya Empire began in which year (approx)?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bodh Gaya</t>
+          <t>273 BCE</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kushinagar</t>
+          <t>200 BCE</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the role of 'Antapala' in Mauryan administration?</t>
+          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Chief priest</t>
+          <t>Shunga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Finance minister</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>150</v>
+        <v>65</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
+          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Devavarman</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Brihadratha</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
+          <t>Who was appointed to promote Dhamma among women?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Yuvrajas</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Rajukas</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Sanghamitras</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>42</v>
+        <v>86</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>What was the primary language of Ashoka’s southern edicts?</t>
+          <t>Who was Ashoka's chief queen?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>121</v>
+        <v>43</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>The Kalinga war took place around which year?</t>
+          <t>What was the key feature of Mauryan pillars?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Red granite</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Sanskrit carvings</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>100 BCE</t>
+          <t>Gold-plated tops</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>75</v>
+        <v>102</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka has how many lions?</t>
+          <t>Who was the son of Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>107</v>
+        <v>8</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
+          <t>After which war did Ashoka convert to Buddhism?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Taxila Revolt</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Battle of Magadha</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>36</v>
+        <v>120</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which of these rivers was near the capital of the Mauryas?</t>
+          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Max Müller</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Alexander Cunningham</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>William Jones</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>61</v>
+        <v>11</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
+          <t>What is the name of the script used in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rock Edict II</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Minor Edict I</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What was Ashoka’s religion before converting to Buddhism?</t>
+          <t>What was the status of women under Mauryan rule?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Highly suppressed</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Animism</t>
+          <t>Equal to men</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ajivika</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What was the profession of Chanakya before becoming a political advisor?</t>
+          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Trader</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>64</v>
+        <v>33</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
+          <t>Which ancient text is believed to describe the Mauryan administration?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Treaty of Magadha</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Treaty of Taxila</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Treaty of Indus</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>140</v>
+        <v>66</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>The Mauryan army was primarily composed of which units?</t>
+          <t>What was the name of the currency used during the Maurya period?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Infantry</t>
+          <t>Rupya</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Niska</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Elephants</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>86</v>
+        <v>58</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Who was Ashoka's chief queen?</t>
+          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Where did Megasthenes reside as a Greek ambassador?</t>
+          <t>Ashoka’s title "Devanampiya" means:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Son of Buddha</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Conqueror of Kalinga</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Lord of Kings</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>133</v>
+        <v>108</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What does the name "Ashoka" literally mean?</t>
+          <t>What was the name of the spy network in Mauryan administration?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Without enemies</t>
+          <t>Sanstha</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>One who shines</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Chaturanga</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Protector of Dharma</t>
+          <t>Vyayam</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>83</v>
+        <v>1</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Which modern Indian state was part of ancient Kalinga?</t>
+          <t>Who was the founder of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>138</v>
+        <v>100</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Ashokan inscription at Girnar is in which modern state?</t>
+          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Became a republic</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Shifted capital</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>108</v>
+        <v>13</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>What was the name of the spy network in Mauryan administration?</t>
+          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sanstha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chaturanga</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vyayam</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Which Buddhist council did Ashoka support?</t>
+          <t>What was the official language of Mauryan administration?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>92</v>
+        <v>129</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Who was appointed to promote Dhamma among women?</t>
+          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Yuvrajas</t>
+          <t>Victory rituals</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Rajukas</t>
+          <t>Coronation rituals</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Sanghamitras</t>
+          <t>Marriage festivals</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88</v>
+        <v>149</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>What was the rank of a provincial governor in Mauryan administration?</t>
+          <t>The Mauryan period marked the beginning of what type of administration?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Feudalism</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mahamatra</t>
+          <t>Guild-based</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>115</v>
+        <v>7</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What was the purpose of Ashoka’s rock edicts?</t>
+          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Religious conversion</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Personal glorification</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Historical record</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>10</v>
+        <v>89</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a Mauryan ruler?</t>
+          <t>The Ashokan edicts were mainly meant to:</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Promote taxation</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Record wars</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Praise deities</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>5</v>
+        <v>77</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>What book did Megasthenes write?</t>
+          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Natya Shastra</t>
+          <t>Economic reforms</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>16</v>
+        <v>141</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
+          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Forts</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Mehrauli</t>
+          <t>Trade routes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Delhi-Topra</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>11</v>
+        <v>62</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>What is the name of the script used in Ashoka's inscriptions?</t>
+          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Which ancient text is believed to describe the Mauryan administration?</t>
+          <t>The term 'Samaharta' in Mauryan administration meant:</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Army general</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Spiritual leader</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>117</v>
+        <v>28</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
+          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>69</v>
+        <v>15</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>How many provinces were there during Ashoka’s reign?</t>
+          <t>What was the profession of Chanakya before becoming a political advisor?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Trader</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>39</v>
+        <v>67</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
+          <t>Which of the following was a major port during Mauryan rule?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bharuch</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Kaveripattinam</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>91</v>
+        <v>128</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
+          <t>Which edict talks about religious tolerance by Ashoka?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Respect for elders</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Minor Rock Edict I</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Religious tolerance</t>
+          <t>Pillar Edict III</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Rock Edict VI</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112</v>
+        <v>32</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is now the emblem of:</t>
+          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>23</v>
+        <v>142</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
+          <t>Who built the first stone Buddhist monuments in India?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
           <t>Bindusara</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="E50" t="inlineStr">
         <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Chandragupta Maurya</t>
-        </is>
-      </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
+          <t>Which profession was supervised during Mauryan times for quality control?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Carpenters</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Doctors</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Blacksmiths</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Which southern kingdom did Ashoka not conquer?</t>
+          <t>Who was the head monk at the Third Buddhist Council?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Ananda</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Pandya</t>
+          <t>Kassapa</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Chera</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which science was advanced under Mauryan rule?</t>
+          <t>The Lion Capital of Ashoka has how many lions?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Metallurgy</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
+          <t>Which profession was part of state control under Mauryan rule?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Medical practice</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
+          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2394,12 +2390,12 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2409,1906 +2405,1910 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who was the founder of the Maurya Empire?</t>
+          <t>Who among the following was not sent as a missionary by Ashoka?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Rakkhita</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>80</v>
+        <v>45</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
+          <t>Which Mauryan ruler was known for religious tolerance?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ashvaghosha</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>6</v>
+        <v>147</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya?</t>
+          <t>Which officer was responsible for maintaining law and order?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>9</v>
+        <v>35</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Which religion did Ashoka promote after the Kalinga War?</t>
+          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Zoroastrianism</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>89</v>
+        <v>10</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>The Ashokan edicts were mainly meant to:</t>
+          <t>Which of the following was NOT a Mauryan ruler?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Promote taxation</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Record wars</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Praise deities</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
+          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Persians</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Egyptians</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>What was the name of the tax collected during the Mauryan rule?</t>
+          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sharada</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Maurya Empire began in which year (approx)?</t>
+          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>273 BCE</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>200 BCE</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
+          <t>What does the name "Ashoka" literally mean?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Without enemies</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>One who shines</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Kaniska</t>
+          <t>Protector of Dharma</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>145</v>
+        <v>84</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Which term referred to a municipal officer under the Mauryas?</t>
+          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mahamattas</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>The term 'Samaharta' in Mauryan administration meant:</t>
+          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Army general</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Persians</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Spiritual leader</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Egyptians</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
+          <t>Which modern Indian state was part of ancient Kalinga?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which natural element was used to polish Mauryan pillars?</t>
+          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Quartz</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>66</v>
+        <v>25</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What was the name of the currency used during the Maurya period?</t>
+          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Rupya</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Niska</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>127</v>
+        <v>52</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
+          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Ibn Battuta</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Marco Polo</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>War strategies</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Territorial expansion</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>99</v>
+        <v>126</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
+          <t>Which branch of philosophy did Chanakya support?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>100</v>
+        <v>51</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
+          <t>What material were most of the Ashokan pillars made from?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Granite</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Sandalwood</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Became a republic</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Shifted capital</t>
+          <t>Marble</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>46</v>
+        <v>88</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
+          <t>What was the rank of a provincial governor in Mauryan administration?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>First Council</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Second Council</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Fourth Council</t>
+          <t>Mahamatra</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>After which war did Ashoka convert to Buddhism?</t>
+          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Taxila Revolt</t>
+          <t>Devavarman</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Brihadratha</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Battle of Magadha</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17</v>
+        <v>137</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Ashokan edict mentions the Kalinga War?</t>
+          <t>Who compiled the Arthashastra?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Minor Pillar Edict I</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pillar Edict VII</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>97</v>
+        <v>2</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
+          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mauryan glaze</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Ashokan polish</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Mirror carving</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Vishnu Gupta</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128</v>
+        <v>106</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which edict talks about religious tolerance by Ashoka?</t>
+          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>War</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Minor Rock Edict I</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pillar Edict III</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Rock Edict VI</t>
+          <t>Victory</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
+          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>4</v>
+        <v>138</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
+          <t>The Ashokan inscription at Girnar is in which modern state?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pliny</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Seleucus</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Who was the head monk at the Third Buddhist Council?</t>
+          <t>Which system did Mauryans follow for currency?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Cowry-based</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Ananda</t>
+          <t>Gold coins</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Kassapa</t>
+          <t>Silver coins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known for religious tolerance?</t>
+          <t>Where did Chandragupta Maurya spend his last years?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
+          <t>The Lion Capital of Ashoka is located at:</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>137</v>
+        <v>22</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Who compiled the Arthashastra?</t>
+          <t>In which language were Ashoka’s inscriptions mostly written?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>51</v>
+        <v>26</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What material were most of the Ashokan pillars made from?</t>
+          <t>Which southern kingdom did Ashoka not conquer?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Granite</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Sandalwood</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Pandya</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Marble</t>
+          <t>Chera</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>What was the status of women under Mauryan rule?</t>
+          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Highly suppressed</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Equal to men</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Ambassadors</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>NGOs</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>22</v>
+        <v>131</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>In which language were Ashoka’s inscriptions mostly written?</t>
+          <t>Who were the Sthanikas in the Mauryan system?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Village guards</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Army commanders</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>35</v>
+        <v>78</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
+          <t>Ashoka sent missionaries to which of the following regions?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Arabia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Tibet</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which profession was part of state control under Mauryan rule?</t>
+          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Medical practice</t>
+          <t>Sudharma</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Which Chinese traveler praised the Mauryan governance?</t>
+          <t>The Mauryan army was primarily composed of which units?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Xuanzang</t>
+          <t>Infantry</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr"/>
+          <t>Elephants</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>All of the above</t>
+        </is>
+      </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>What administrative division existed under Maurya rule?</t>
+          <t>Which religion did Ashoka promote after the Kalinga War?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Janapadas</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Mahajanapadas</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Districts</t>
+          <t>Zoroastrianism</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>71</v>
+        <v>97</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
+          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Mauryan glaze</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Ashokan polish</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Mirror carving</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>144</v>
+        <v>46</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
+          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>First Council</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Second Council</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Fourth Council</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>67</v>
+        <v>139</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which of the following was a major port during Mauryan rule?</t>
+          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Bharuch</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Kaveripattinam</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>72</v>
+        <v>56</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>What was the official language of Mauryan administration?</t>
+          <t>Which Mauryan king followed Jainism in his later life?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>81</v>
+        <v>12</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
+          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bactria</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
+          <t>Which city served as the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Persian king</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Roman emperor</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Egyptian Pharaoh</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>27</v>
+        <v>80</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
+          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Ashvaghosha</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Where did Chandragupta Maurya spend his last years?</t>
+          <t>What was the main focus of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Military expansion</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Religious conversions</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
+          <t>What was the purpose of Ashoka’s rock edicts?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Religious conversion</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Personal glorification</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Historical record</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What was the capital of the Maurya Empire?</t>
+          <t>What book did Megasthenes write?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Natya Shastra</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>82</v>
+        <v>114</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
+          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>53</v>
+        <v>110</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>What was the main source of revenue in Mauryan administration?</t>
+          <t>The Sanchi Stupa was originally commissioned by:</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>94</v>
+        <v>136</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
+          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Western India</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Coastal India</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
+          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>87</v>
+        <v>31</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which profession was supervised during Mauryan times for quality control?</t>
+          <t>What was the name of the tax collected during the Mauryan rule?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Doctors</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Blacksmiths</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Sharada</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>40</v>
+        <v>113</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
+          <t>What was Ashoka’s religion before converting to Buddhism?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Animism</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Sudharma</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Ajivika</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Who were the Sthanikas in the Mauryan system?</t>
+          <t>Which science was advanced under Mauryan rule?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Village guards</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Army commanders</t>
+          <t>Metallurgy</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Which city served as the capital of the Maurya Empire?</t>
+          <t>Where did Megasthenes reside as a Greek ambassador?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
+          <t>Taxila</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
           <t>Patliputra</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>Ujjain</t>
-        </is>
-      </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -4320,371 +4320,371 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler gave up violence completely?</t>
+          <t>Which Ashokan edict mentions the Kalinga War?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Minor Pillar Edict I</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Pillar Edict VII</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>102</v>
+        <v>54</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Who was the son of Chandragupta Maurya?</t>
+          <t>The Maurya Empire was established in which century BCE?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>106</v>
+        <v>79</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
+          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>49</v>
+        <v>91</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Ashoka’s title "Devanampiya" means:</t>
+          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Son of Buddha</t>
+          <t>Respect for elders</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Conqueror of Kalinga</t>
+          <t>Religious tolerance</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lord of Kings</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
+          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Economic reforms</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
+          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Western India</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Coastal India</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129</v>
+        <v>69</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
+          <t>How many provinces were there during Ashoka’s reign?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Victory rituals</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Coronation rituals</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Marriage festivals</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>139</v>
+        <v>59</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
+          <t>Who succeeded Ashoka as emperor?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
+          <t>Dasharatha</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Kunala</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
           <t>Bindusara</t>
         </is>
       </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>Ashoka</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
+      <c r="G116" t="inlineStr">
         <is>
           <t>Dasharatha</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>Ashoka</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>The Sanchi Stupa was originally commissioned by:</t>
+          <t>Which Buddhist council did Ashoka support?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
+          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>34</v>
+        <v>98</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is located at:</t>
+          <t>Which site has a monolithic Ashokan elephant statue?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4694,835 +4694,835 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Rampurva</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Kumhrar</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>54</v>
+        <v>27</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>The Maurya Empire was established in which century BCE?</t>
+          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
+          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Responsible for judiciary</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Pliny</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Minister of religion</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Advisor to Emperor</t>
+          <t>Seleucus</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>78</v>
+        <v>112</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Ashoka sent missionaries to which of the following regions?</t>
+          <t>The Lion Capital of Ashoka is now the emblem of:</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Arabia</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tibet</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>122</v>
+        <v>145</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which king was known as “Ashoka the Great”?</t>
+          <t>Which term referred to a municipal officer under the Mauryas?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Mahamattas</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Which branch of philosophy did Chanakya support?</t>
+          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vedanta</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Kaniska</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
+          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Shunga</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>76</v>
+        <v>124</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
+          <t>Which natural element was used to polish Mauryan pillars?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Indica</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Quartz</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mahabhashya</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>20</v>
+        <v>125</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
+          <t>Which Mauryan emperor ruled the longest?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>44</v>
+        <v>16</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
+          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Mehrauli</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Delhi-Topra</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which title did Ashoka use for himself in inscriptions?</t>
+          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Samrat</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Rock Edict III</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Maharajadhiraja</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
+          <t>Which title did Ashoka use for himself in inscriptions?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Samrat</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Maharajadhiraja</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
+          <t>What was the main source of revenue in Mauryan administration?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Expansion of navy</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Increase in cavalry</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Recruitment from Kalinga</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>28</v>
+        <v>127</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
+          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>War strategies</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Territorial expansion</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>149</v>
+        <v>121</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The Mauryan period marked the beginning of what type of administration?</t>
+          <t>The Kalinga war took place around which year?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Feudalism</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Guild-based</t>
+          <t>100 BCE</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>19</v>
+        <v>82</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>What was the main focus of Ashoka’s Dhamma?</t>
+          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Military expansion</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Religious conversions</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>29</v>
+        <v>95</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ashoka’s policy after the Kalinga war was called?</t>
+          <t>Which area was not fully controlled by the Mauryas?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Rajadharma</t>
+          <t>Deccan</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Ahimsa</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Sangha</t>
+          <t>Kashmir</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>56</v>
+        <v>143</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which Mauryan king followed Jainism in his later life?</t>
+          <t>Which son of Ashoka ruled the western part of the empire?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sumana</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>47</v>
+        <v>132</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Where was the Third Buddhist Council held?</t>
+          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Minor Rock Edict</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which of the following was a key feature of Mauryan administration?</t>
+          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Feudal system</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tribal governance</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Decentralized rule</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>98</v>
+        <v>68</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which site has a monolithic Ashokan elephant statue?</t>
+          <t>What administrative division existed under Maurya rule?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Janapadas</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Rampurva</t>
+          <t>Mahajanapadas</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Kumhrar</t>
+          <t>Districts</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>63</v>
+        <v>144</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
+          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
+          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
+          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Rock Edict II</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Rock Edict III</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5532,336 +5532,336 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Minor Edict I</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>132</v>
+        <v>6</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
+          <t>Who succeeded Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Minor Rock Edict</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>141</v>
+        <v>122</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
+          <t>Which king was known as “Ashoka the Great”?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Forts</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Trade routes</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which son of Ashoka ruled the western part of the empire?</t>
+          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Treaty of Magadha</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Treaty of Taxila</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Sumana</t>
+          <t>Treaty of Indus</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>What was the key feature of Mauryan pillars?</t>
+          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Red granite</t>
+          <t>Expansion of navy</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Sanskrit carvings</t>
+          <t>Increase in cavalry</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Gold-plated tops</t>
+          <t>Recruitment from Kalinga</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>118</v>
+        <v>47</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Which system did Mauryans follow for currency?</t>
+          <t>Where was the Third Buddhist Council held?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Cowry-based</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Gold coins</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Silver coins</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
+          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Persian king</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>Roman emperor</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Egyptian Pharaoh</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Which dynasty succeeded the Maurya Empire?</t>
+          <t>Ashoka’s policy after the Kalinga war was called?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Rajadharma</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Ahimsa</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Sangha</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
+          <t>Which of these rivers was near the capital of the Mauryas?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ibn Battuta</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Marco Polo</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>125</v>
+        <v>76</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor ruled the longest?</t>
+          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Indica</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Mahabhashya</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>

--- a/Data/mauryaEmpire.xlsx
+++ b/Data/mauryaEmpire.xlsx
@@ -472,320 +472,324 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Which Chinese traveler praised the Mauryan governance?</t>
+          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Xuanzang</t>
+          <t>War</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr"/>
+          <t>Unity</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Victory</t>
+        </is>
+      </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>71</v>
+        <v>19</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
+          <t>What was the main focus of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Military expansion</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Religious conversions</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which of the following was a key feature of Mauryan administration?</t>
+          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Feudal system</t>
+          <t>Ibn Battuta</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Marco Polo</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Tribal governance</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Decentralized rule</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
+          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Forts</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Trade routes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>44</v>
+        <v>6</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
+          <t>Who succeeded Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>42</v>
+        <v>115</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What was the primary language of Ashoka’s southern edicts?</t>
+          <t>What was the purpose of Ashoka’s rock edicts?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Religious conversion</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Personal glorification</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Historical record</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>14</v>
+        <v>45</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which dynasty succeeded the Maurya Empire?</t>
+          <t>Which Mauryan ruler was known for religious tolerance?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>57</v>
+        <v>91</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>What was the role of 'Antapala' in Mauryan administration?</t>
+          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Chief priest</t>
+          <t>Respect for elders</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Religious tolerance</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Finance minister</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
+          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Responsible for judiciary</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minister of religion</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Advisor to Emperor</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
@@ -828,1384 +832,1384 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>39</v>
+        <v>99</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
+          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which city did Ashoka develop into a major Buddhist center?</t>
+          <t>Which city served as the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Bodh Gaya</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kushinagar</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>3</v>
+        <v>136</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>What was the capital of the Maurya Empire?</t>
+          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
+          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bactria</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Became a republic</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Shifted capital</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>96</v>
+        <v>59</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>The Maurya Empire began in which year (approx)?</t>
+          <t>Who succeeded Ashoka as emperor?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>273 BCE</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>200 BCE</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>103</v>
+        <v>53</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
+          <t>What was the main source of revenue in Mauryan administration?</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Shunga</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
+          <t>What book did Megasthenes write?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>Natya Shastra</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>92</v>
+        <v>20</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Who was appointed to promote Dhamma among women?</t>
+          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Yuvrajas</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rajukas</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sanghamitras</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Who was Ashoka's chief queen?</t>
+          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>War strategies</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Territorial expansion</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>43</v>
+        <v>57</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What was the key feature of Mauryan pillars?</t>
+          <t>What was the role of 'Antapala' in Mauryan administration?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Red granite</t>
+          <t>Chief priest</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Sanskrit carvings</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Gold-plated tops</t>
+          <t>Finance minister</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>102</v>
+        <v>56</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Who was the son of Chandragupta Maurya?</t>
+          <t>Which Mauryan king followed Jainism in his later life?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dasharatha</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Chandragupta Maurya</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Dasharatha</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bimbisara</t>
-        </is>
-      </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>After which war did Ashoka convert to Buddhism?</t>
+          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Taxila Revolt</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Battle of Magadha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>120</v>
+        <v>147</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
+          <t>Which officer was responsible for maintaining law and order?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Alexander Cunningham</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>William Jones</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>11</v>
+        <v>25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>What is the name of the script used in Ashoka's inscriptions?</t>
+          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>What was the status of women under Mauryan rule?</t>
+          <t>Who were the Sthanikas in the Mauryan system?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Highly suppressed</t>
+          <t>Village guards</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Equal to men</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Army commanders</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
+          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Treaty of Magadha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Treaty of Taxila</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>Treaty of Indus</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>33</v>
+        <v>97</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Which ancient text is believed to describe the Mauryan administration?</t>
+          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Mauryan glaze</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Ashokan polish</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Mirror carving</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>What was the name of the currency used during the Maurya period?</t>
+          <t>Who was the head monk at the Third Buddhist Council?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Rupya</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Niska</t>
+          <t>Ananda</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Kassapa</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>58</v>
+        <v>21</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
+          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Ashoka’s title "Devanampiya" means:</t>
+          <t>The term 'Samaharta' in Mauryan administration meant:</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Son of Buddha</t>
+          <t>Army general</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Conqueror of Kalinga</t>
+          <t>Spiritual leader</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lord of Kings</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>What was the name of the spy network in Mauryan administration?</t>
+          <t>Where did Megasthenes reside as a Greek ambassador?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sanstha</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Chaturanga</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vyayam</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1</v>
+        <v>120</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who was the founder of the Maurya Empire?</t>
+          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Max Müller</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Alexander Cunningham</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>William Jones</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
+          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Became a republic</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Shifted capital</t>
+          <t>Vishnu Gupta</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
+          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Persian</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>What was the official language of Mauryan administration?</t>
+          <t>The Lion Capital of Ashoka has how many lions?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129</v>
+        <v>113</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
+          <t>What was Ashoka’s religion before converting to Buddhism?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Victory rituals</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Animism</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Coronation rituals</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Marriage festivals</t>
+          <t>Ajivika</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>149</v>
+        <v>23</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Mauryan period marked the beginning of what type of administration?</t>
+          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Feudalism</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Guild-based</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>7</v>
+        <v>96</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
+          <t>The Maurya Empire began in which year (approx)?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>273 BCE</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>200 BCE</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>89</v>
+        <v>51</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>The Ashokan edicts were mainly meant to:</t>
+          <t>What material were most of the Ashokan pillars made from?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Promote taxation</t>
+          <t>Granite</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Record wars</t>
+          <t>Sandalwood</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Praise deities</t>
+          <t>Marble</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>77</v>
+        <v>134</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
+          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Economic reforms</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>141</v>
+        <v>11</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
+          <t>What is the name of the script used in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Forts</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Trade routes</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>62</v>
+        <v>143</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
+          <t>Which son of Ashoka ruled the western part of the empire?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Sumana</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>38</v>
+        <v>88</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>The term 'Samaharta' in Mauryan administration meant:</t>
+          <t>What was the rank of a provincial governor in Mauryan administration?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Army general</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Spiritual leader</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Mahamatra</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>28</v>
+        <v>146</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
+          <t>What was the status of women under Mauryan rule?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Highly suppressed</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Equal to men</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>15</v>
+        <v>109</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>What was the profession of Chanakya before becoming a political advisor?</t>
+          <t>Which Buddhist council did Ashoka support?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trader</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>67</v>
+        <v>36</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of the following was a major port during Mauryan rule?</t>
+          <t>Which of these rivers was near the capital of the Mauryas?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Bharuch</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kaveripattinam</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128</v>
+        <v>150</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Which edict talks about religious tolerance by Ashoka?</t>
+          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Minor Rock Edict I</t>
+          <t>Devavarman</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Pillar Edict III</t>
+          <t>Brihadratha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rock Edict VI</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
+          <t>Which science was advanced under Mauryan rule?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Metallurgy</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Who built the first stone Buddhist monuments in India?</t>
+          <t>Which of the following was NOT a Mauryan ruler?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2220,184 +2224,184 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Harsha</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>87</v>
+        <v>67</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which profession was supervised during Mauryan times for quality control?</t>
+          <t>Which of the following was a major port during Mauryan rule?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Doctors</t>
+          <t>Bharuch</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Blacksmiths</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Kaveripattinam</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Who was the head monk at the Third Buddhist Council?</t>
+          <t>The Maurya Empire was established in which century BCE?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Ananda</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Kassapa</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka has how many lions?</t>
+          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Sudharma</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Which profession was part of state control under Mauryan rule?</t>
+          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Medical practice</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Kaniska</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>23</v>
+        <v>139</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
+          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
           <t>Bindusara</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="E55" t="inlineStr">
         <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>Chandragupta Maurya</t>
-        </is>
-      </c>
       <c r="F55" t="inlineStr">
         <is>
           <t>Dasharatha</t>
@@ -2405,1648 +2409,1648 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Who among the following was not sent as a missionary by Ashoka?</t>
+          <t>Which religion did Ashoka promote after the Kalinga War?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rakkhita</t>
+          <t>Zoroastrianism</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>45</v>
+        <v>149</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known for religious tolerance?</t>
+          <t>The Mauryan period marked the beginning of what type of administration?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Feudalism</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Guild-based</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>147</v>
+        <v>60</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Which officer was responsible for maintaining law and order?</t>
+          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
+          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Responsible for judiciary</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Minister of religion</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Advisor to Emperor</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a Mauryan ruler?</t>
+          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
+          <t>What was the primary language of Ashoka’s southern edicts?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>21</v>
+        <v>128</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
+          <t>Which edict talks about religious tolerance by Ashoka?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Minor Rock Edict I</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Pillar Edict III</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Rock Edict VI</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>116</v>
+        <v>66</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
+          <t>What was the name of the currency used during the Maurya period?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Rupya</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Niska</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>133</v>
+        <v>22</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>What does the name "Ashoka" literally mean?</t>
+          <t>In which language were Ashoka’s inscriptions mostly written?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Without enemies</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>One who shines</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Protector of Dharma</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>84</v>
+        <v>108</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
+          <t>What was the name of the spy network in Mauryan administration?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Sanstha</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Chaturanga</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Vyayam</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>90</v>
+        <v>117</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
+          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Persians</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Egyptians</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which modern Indian state was part of ancient Kalinga?</t>
+          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>123</v>
+        <v>72</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
+          <t>What was the official language of Mauryan administration?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
+          <t>What was the key feature of Mauryan pillars?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Red granite</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Sanskrit carvings</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Gold-plated tops</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>52</v>
+        <v>77</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
+          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Ibn Battuta</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Marco Polo</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Economic reforms</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Which branch of philosophy did Chanakya support?</t>
+          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Persian king</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Vedanta</t>
+          <t>Roman emperor</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Egyptian Pharaoh</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>51</v>
+        <v>129</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>What material were most of the Ashokan pillars made from?</t>
+          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Granite</t>
+          <t>Victory rituals</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Sandalwood</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Coronation rituals</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marble</t>
+          <t>Marriage festivals</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>What was the rank of a provincial governor in Mauryan administration?</t>
+          <t>Which profession was supervised during Mauryan times for quality control?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Carpenters</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Doctors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Blacksmiths</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mahamatra</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>150</v>
+        <v>34</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
+          <t>The Lion Capital of Ashoka is located at:</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Devavarman</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Brihadratha</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>137</v>
+        <v>17</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Who compiled the Arthashastra?</t>
+          <t>Which Ashokan edict mentions the Kalinga War?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Minor Pillar Edict I</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Pillar Edict VII</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2</v>
+        <v>58</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
+          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vishnu Gupta</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
+          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Bactria</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>117</v>
+        <v>33</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
+          <t>Which ancient text is believed to describe the Mauryan administration?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>138</v>
+        <v>83</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>The Ashokan inscription at Girnar is in which modern state?</t>
+          <t>Which modern Indian state was part of ancient Kalinga?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
+          <t>Assam</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
           <t>Odisha</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Gujarat</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Which system did Mauryans follow for currency?</t>
+          <t>The Lion Capital of Ashoka is now the emblem of:</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cowry-based</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Gold coins</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Silver coins</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Where did Chandragupta Maurya spend his last years?</t>
+          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is located at:</t>
+          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>In which language were Ashoka’s inscriptions mostly written?</t>
+          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>26</v>
+        <v>68</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Which southern kingdom did Ashoka not conquer?</t>
+          <t>What administrative division existed under Maurya rule?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Janapadas</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Pandya</t>
+          <t>Mahajanapadas</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Chera</t>
+          <t>Districts</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>148</v>
+        <v>78</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
+          <t>Ashoka sent missionaries to which of the following regions?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ambassadors</t>
+          <t>Arabia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>NGOs</t>
+          <t>Tibet</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131</v>
+        <v>89</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Who were the Sthanikas in the Mauryan system?</t>
+          <t>The Ashokan edicts were mainly meant to:</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Village guards</t>
+          <t>Promote taxation</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Record wars</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Army commanders</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Praise deities</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>78</v>
+        <v>14</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ashoka sent missionaries to which of the following regions?</t>
+          <t>Which dynasty succeeded the Maurya Empire?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Arabia</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tibet</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
+          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Sudharma</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>140</v>
+        <v>13</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>The Mauryan army was primarily composed of which units?</t>
+          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Infantry</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Elephants</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>9</v>
+        <v>90</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Which religion did Ashoka promote after the Kalinga War?</t>
+          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Persians</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zoroastrianism</t>
+          <t>Egyptians</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
+          <t>Which site has a monolithic Ashokan elephant statue?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Mauryan glaze</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Ashokan polish</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Mirror carving</t>
+          <t>Rampurva</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Kumhrar</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>46</v>
+        <v>92</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
+          <t>Who was appointed to promote Dhamma among women?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>First Council</t>
+          <t>Yuvrajas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Second Council</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Rajukas</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Fourth Council</t>
+          <t>Sanghamitras</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>139</v>
+        <v>7</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
+          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which Mauryan king followed Jainism in his later life?</t>
+          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Indica</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Mahabhashya</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>12</v>
+        <v>86</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
+          <t>Who was Ashoka's chief queen?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>101</v>
+        <v>82</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which city served as the capital of the Maurya Empire?</t>
+          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>80</v>
+        <v>114</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
+          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Ashvaghosha</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>What was the main focus of Ashoka’s Dhamma?</t>
+          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Military expansion</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Religious conversions</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Western India</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Coastal India</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>115</v>
+        <v>29</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>What was the purpose of Ashoka’s rock edicts?</t>
+          <t>Ashoka’s policy after the Kalinga war was called?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Religious conversion</t>
+          <t>Rajadharma</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Personal glorification</t>
+          <t>Ahimsa</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Historical record</t>
+          <t>Sangha</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>5</v>
+        <v>102</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>What book did Megasthenes write?</t>
+          <t>Who was the son of Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Natya Shastra</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
+          <t>Which area was not fully controlled by the Mauryas?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Deccan</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4056,851 +4060,847 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Kashmir</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>110</v>
+        <v>46</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>The Sanchi Stupa was originally commissioned by:</t>
+          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>First Council</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Second Council</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Fourth Council</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
+          <t>How many provinces were there during Ashoka’s reign?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
+          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>31</v>
+        <v>118</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>What was the name of the tax collected during the Mauryan rule?</t>
+          <t>Which system did Mauryans follow for currency?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Cowry-based</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Gold coins</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Silver coins</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Sharada</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What was Ashoka’s religion before converting to Buddhism?</t>
+          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Animism</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Ajivika</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>74</v>
+        <v>26</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which science was advanced under Mauryan rule?</t>
+          <t>Which southern kingdom did Ashoka not conquer?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Metallurgy</t>
+          <t>Pandya</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chera</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Where did Megasthenes reside as a Greek ambassador?</t>
+          <t>Ashoka’s title "Devanampiya" means:</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Son of Buddha</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Conqueror of Kalinga</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Lord of Kings</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which Ashokan edict mentions the Kalinga War?</t>
+          <t>Which Mauryan emperor ruled the longest?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Minor Pillar Edict I</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Pillar Edict VII</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>The Maurya Empire was established in which century BCE?</t>
+          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
+          <t>The Kalinga war took place around which year?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>100 BCE</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>91</v>
+        <v>24</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
+          <t>Where did Chandragupta Maurya spend his last years?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Respect for elders</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Religious tolerance</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134</v>
+        <v>85</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
+          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict III</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>94</v>
+        <v>122</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
+          <t>Which king was known as “Ashoka the Great”?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Western India</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Coastal India</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>69</v>
+        <v>104</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>How many provinces were there during Ashoka’s reign?</t>
+          <t>Which title did Ashoka use for himself in inscriptions?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Samrat</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Maharajadhiraja</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>59</v>
+        <v>132</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Who succeeded Ashoka as emperor?</t>
+          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Minor Rock Edict</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>109</v>
+        <v>1</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Which Buddhist council did Ashoka support?</t>
+          <t>Who was the founder of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>70</v>
+        <v>119</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
+          <t>Which Chinese traveler praised the Mauryan governance?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Xuanzang</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Lion</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>Elephant</t>
-        </is>
-      </c>
+          <t>Megasthenes</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>98</v>
+        <v>107</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which site has a monolithic Ashokan elephant statue?</t>
+          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Rampurva</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Kumhrar</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
+          <t>Which city did Ashoka develop into a major Buddhist center?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bodh Gaya</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Kushinagar</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
+          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Ashvaghosha</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Pliny</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Seleucus</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is now the emblem of:</t>
+          <t>The Sanchi Stupa was originally commissioned by:</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Which term referred to a municipal officer under the Mauryas?</t>
+          <t>What does the name "Ashoka" literally mean?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Without enemies</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>One who shines</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Mahamattas</t>
+          <t>Protector of Dharma</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>111</v>
+        <v>84</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
+          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Kaniska</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>99</v>
+        <v>142</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
+          <t>Who built the first stone Buddhist monuments in India?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4915,544 +4915,544 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124</v>
+        <v>137</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Which natural element was used to polish Mauryan pillars?</t>
+          <t>Who compiled the Arthashastra?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Quartz</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>125</v>
+        <v>31</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor ruled the longest?</t>
+          <t>What was the name of the tax collected during the Mauryan rule?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Sharada</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
+          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mehrauli</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Delhi-Topra</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>85</v>
+        <v>30</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
+          <t>Which of the following was a key feature of Mauryan administration?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Feudal system</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Rock Edict III</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Tribal governance</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Decentralized rule</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>104</v>
+        <v>16</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which title did Ashoka use for himself in inscriptions?</t>
+          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Samrat</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Mehrauli</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Maharajadhiraja</t>
+          <t>Delhi-Topra</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>What was the main source of revenue in Mauryan administration?</t>
+          <t>Who among the following was not sent as a missionary by Ashoka?</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Rakkhita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>127</v>
+        <v>47</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
+          <t>Where was the Third Buddhist Council held?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>War strategies</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Territorial expansion</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>121</v>
+        <v>4</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>The Kalinga war took place around which year?</t>
+          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Pliny</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>100 BCE</t>
+          <t>Seleucus</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>82</v>
+        <v>130</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
+          <t>Which profession was part of state control under Mauryan rule?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Medical practice</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>95</v>
+        <v>138</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Which area was not fully controlled by the Mauryas?</t>
+          <t>The Ashokan inscription at Girnar is in which modern state?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Deccan</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Kashmir</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Which son of Ashoka ruled the western part of the empire?</t>
+          <t>After which war did Ashoka convert to Buddhism?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Taxila Revolt</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Sumana</t>
+          <t>Battle of Magadha</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>132</v>
+        <v>27</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
+          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Minor Rock Edict</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
+          <t>Which term referred to a municipal officer under the Mauryas?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Mahamattas</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>68</v>
+        <v>148</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>What administrative division existed under Maurya rule?</t>
+          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Janapadas</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mahajanapadas</t>
+          <t>Ambassadors</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Districts</t>
+          <t>NGOs</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
+          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>Chandragupta</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
       <c r="E140" t="inlineStr">
         <is>
           <t>Ashoka</t>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -5472,396 +5472,396 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>63</v>
+        <v>103</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
+          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Shunga</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
+          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Rock Edict II</t>
+          <t>Expansion of navy</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Increase in cavalry</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Minor Edict I</t>
+          <t>Recruitment from Kalinga</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>6</v>
+        <v>61</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya?</t>
+          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rock Edict II</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Minor Edict I</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which king was known as “Ashoka the Great”?</t>
+          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>64</v>
+        <v>124</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
+          <t>Which natural element was used to polish Mauryan pillars?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Treaty of Magadha</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Treaty of Taxila</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Quartz</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Treaty of Indus</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>50</v>
+        <v>15</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
+          <t>What was the profession of Chanakya before becoming a political advisor?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Expansion of navy</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Increase in cavalry</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Trader</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Recruitment from Kalinga</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Where was the Third Buddhist Council held?</t>
+          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
+          <t>Which branch of philosophy did Chanakya support?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Persian king</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Roman emperor</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Egyptian Pharaoh</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>29</v>
+        <v>140</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Ashoka’s policy after the Kalinga war was called?</t>
+          <t>The Mauryan army was primarily composed of which units?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Rajadharma</t>
+          <t>Infantry</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Ahimsa</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Elephants</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Sangha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Which of these rivers was near the capital of the Mauryas?</t>
+          <t>What was the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
+          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Indica</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Mahabhashya</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>

--- a/Data/mauryaEmpire.xlsx
+++ b/Data/mauryaEmpire.xlsx
@@ -472,1415 +472,1415 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
+          <t>Where was the Third Buddhist Council held?</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>War</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Vaishali</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Unity</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Victory</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Law of Dharma</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>19</v>
+        <v>95</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>What was the main focus of Ashoka’s Dhamma?</t>
+          <t>Which area was not fully controlled by the Mauryas?</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Military expansion</t>
+          <t>Deccan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Religious conversions</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Kashmir</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Moral values and social harmony</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
+          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ibn Battuta</t>
+          <t>Expansion of navy</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Marco Polo</t>
+          <t>Increase in cavalry</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fa-Hien</t>
+          <t>Recruitment from Kalinga</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Shift to non-violence</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>141</v>
+        <v>34</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
+          <t>The Lion Capital of Ashoka is located at:</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Forts</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Temples</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Trade routes</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Buddhist monasteries</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>6</v>
+        <v>91</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya?</t>
+          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Respect for elders</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Religious tolerance</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Charity</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Animal sacrifice</t>
         </is>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>What was the purpose of Ashoka’s rock edicts?</t>
+          <t>What was the official language of Mauryan administration?</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Religious conversion</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Personal glorification</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Historical record</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Moral instructions</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known for religious tolerance?</t>
+          <t>Which religion did Ashoka promote after the Kalinga War?</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Zoroastrianism</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a part of Ashoka’s Dhamma?</t>
+          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Respect for elders</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Religious tolerance</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Charity</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Animal sacrifice</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>44</v>
+        <v>98</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
+          <t>Which site has a monolithic Ashokan elephant statue?</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Rampurva</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Kumhrar</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Dhauli</t>
         </is>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler gave up violence completely?</t>
+          <t>The Kalinga war took place around which year?</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>100 BCE</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>261 BCE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99</v>
+        <v>41</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
+          <t>Which city did Ashoka develop into a major Buddhist center?</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Lumbini</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bodh Gaya</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Kushinagar</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Sanchi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>101</v>
+        <v>115</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Which city served as the capital of the Maurya Empire?</t>
+          <t>What was the purpose of Ashoka’s rock edicts?</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Varanasi</t>
+          <t>Religious conversion</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Personal glorification</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Historical record</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Moral instructions</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136</v>
+        <v>63</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
+          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Rajagriha</t>
+          <t>3</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>4</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
+          <t>Which ruler sent Ashoka to suppress the Taxila revolt?</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Expanded</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Became a republic</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Shifted capital</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Collapsed quickly</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>59</v>
+        <v>30</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Who succeeded Ashoka as emperor?</t>
+          <t>Which of the following was a key feature of Mauryan administration?</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Feudal system</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Tribal governance</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Decentralized rule</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>53</v>
+        <v>89</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>What was the main source of revenue in Mauryan administration?</t>
+          <t>The Ashokan edicts were mainly meant to:</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Promote taxation</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Record wars</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Trade</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Donations</t>
+          <t>Praise deities</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Agriculture</t>
+          <t>Instruct citizens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>What book did Megasthenes write?</t>
+          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Natya Shastra</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Indika</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>20</v>
+        <v>61</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
+          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Rock Edict II</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Rome</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Minor Edict I</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127</v>
+        <v>78</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
+          <t>Ashoka sent missionaries to which of the following regions?</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>War strategies</t>
+          <t>Arabia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Territorial expansion</t>
+          <t>Tibet</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Moral governance</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>What was the role of 'Antapala' in Mauryan administration?</t>
+          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Chief priest</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Village head</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Finance minister</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Border security official</t>
+          <t>Magadhi</t>
         </is>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Which Mauryan king followed Jainism in his later life?</t>
+          <t>Who was the son of Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
+          <t>Ashoka</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Dasharatha</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>Bindusara</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Dasharatha</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>Chandragupta Maurya</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135</v>
+        <v>46</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
+          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>First Council</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Second Council</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Fourth Council</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Third Council</t>
         </is>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>147</v>
+        <v>44</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Which officer was responsible for maintaining law and order?</t>
+          <t>What animal is depicted at the base of Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>25</v>
+        <v>94</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
+          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Southern India</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Western India</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Coastal India</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Northern India</t>
         </is>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131</v>
+        <v>8</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Who were the Sthanikas in the Mauryan system?</t>
+          <t>After which war did Ashoka convert to Buddhism?</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Village guards</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Taxila Revolt</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Army commanders</t>
+          <t>Battle of Hydaspes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Priests</t>
+          <t>Battle of Magadha</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tax collectors</t>
+          <t>Kalinga War</t>
         </is>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
+          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Treaty of Magadha</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Treaty of Taxila</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Treaty of Indus</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Treaty of Patliputra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>97</v>
+        <v>141</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
+          <t>Ashoka’s Minor Rock Edicts were often located near what?</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Mauryan glaze</t>
+          <t>Forts</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Ashokan polish</t>
+          <t>Temples</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Mirror carving</t>
+          <t>Trade routes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Mauryan polish</t>
+          <t>Buddhist monasteries</t>
         </is>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>48</v>
+        <v>118</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Who was the head monk at the Third Buddhist Council?</t>
+          <t>Which system did Mauryans follow for currency?</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Cowry-based</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Ananda</t>
+          <t>Gold coins</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kassapa</t>
+          <t>Silver coins</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Moggaliputta Tissa</t>
+          <t>Punch-marked coins</t>
         </is>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
+          <t>The Maurya Empire began in which year (approx)?</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>273 BCE</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>185 BCE</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>200 BCE</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>321 BCE</t>
         </is>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>38</v>
+        <v>92</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The term 'Samaharta' in Mauryan administration meant:</t>
+          <t>Who was appointed to promote Dhamma among women?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Army general</t>
+          <t>Yuvrajas</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Spiritual leader</t>
+          <t>Rajukas</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Judge</t>
+          <t>Sanghamitras</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tax collector</t>
+          <t>Mahamatras</t>
         </is>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>73</v>
+        <v>39</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Where did Megasthenes reside as a Greek ambassador?</t>
+          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kashi</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
+          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Max Müller</t>
+          <t>Rock Edict V</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Alexander Cunningham</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>William Jones</t>
+          <t>Minor Rock Edict</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>James Prinsep</t>
+          <t>Pillar Edict IV</t>
         </is>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
+          <t>Which of these rivers was near the capital of the Mauryas?</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vishnu Gupta</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>71</v>
+        <v>150</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
+          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Egyptian</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Roman</t>
+          <t>Devavarman</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Persian</t>
+          <t>Brihadratha</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Kunal</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Greek</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka has how many lions?</t>
+          <t>What book did Megasthenes write?</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Natya Shastra</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Indika</t>
         </is>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>What was Ashoka’s religion before converting to Buddhism?</t>
+          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Bactria</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Animism</t>
+          <t>Armenia</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ajivika</t>
+          <t>Syria</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Afghanistan</t>
         </is>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>23</v>
+        <v>66</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor abdicated his throne and became a Jain monk?</t>
+          <t>What was the name of the currency used during the Maurya period?</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Rupya</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Niska</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Dinar</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Pana</t>
         </is>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Maurya Empire began in which year (approx)?</t>
+          <t>What does the Ashokan Chakra in the Indian flag represent?</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>War</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>273 BCE</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Unity</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>200 BCE</t>
+          <t>Victory</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Law of Dharma</t>
         </is>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>51</v>
+        <v>70</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>What material were most of the Ashokan pillars made from?</t>
+          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Granite</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Sandalwood</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Marble</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Chunar sandstone</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134</v>
+        <v>27</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor had diplomatic contact with Egypt?</t>
+          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1905,2625 +1905,2621 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>What is the name of the script used in Ashoka's inscriptions?</t>
+          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Devanagari</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Madhya Pradesh</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>143</v>
+        <v>64</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Which son of Ashoka ruled the western part of the empire?</t>
+          <t>What was the name of the treaty between Seleucus and Chandragupta?</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kunala</t>
+          <t>Treaty of Magadha</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Treaty of Taxila</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Sumana</t>
+          <t>Treaty of Indus</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tivala</t>
+          <t>Treaty of Patliputra</t>
         </is>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>What was the rank of a provincial governor in Mauryan administration?</t>
+          <t>Which natural element was used to polish Mauryan pillars?</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Sand</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Yuvraja</t>
+          <t>Clay</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Amatya</t>
+          <t>Quartz</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Mahamatra</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kumara</t>
+          <t>Animal fat</t>
         </is>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>146</v>
+        <v>57</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>What was the status of women under Mauryan rule?</t>
+          <t>What was the role of 'Antapala' in Mauryan administration?</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Highly suppressed</t>
+          <t>Chief priest</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Equal to men</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Village head</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Not mentioned</t>
+          <t>Finance minister</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Varied by class</t>
+          <t>Border security official</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>109</v>
+        <v>12</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Which Buddhist council did Ashoka support?</t>
+          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>First</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Second</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Fourth</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Third</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>36</v>
+        <v>90</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Which of these rivers was near the capital of the Mauryas?</t>
+          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Romans</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Persians</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Egyptians</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Greeks</t>
         </is>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>150</v>
+        <v>136</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Ashoka’s grandson, who ruled after Dasharatha, was:</t>
+          <t>Which Mauryan city was a key trading hub with foreign merchants?</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Devavarman</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Brihadratha</t>
+          <t>Rajagriha</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Kunal</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>74</v>
+        <v>11</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Which science was advanced under Mauryan rule?</t>
+          <t>What is the name of the script used in Ashoka's inscriptions?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Medicine</t>
+          <t>Devanagari</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Astronomy</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Metallurgy</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>10</v>
+        <v>138</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Which of the following was NOT a Mauryan ruler?</t>
+          <t>The Ashokan inscription at Girnar is in which modern state?</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Ajatashatru</t>
+          <t>Gujarat</t>
         </is>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>67</v>
+        <v>109</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Which of the following was a major port during Mauryan rule?</t>
+          <t>Which Buddhist council did Ashoka support?</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lothal</t>
+          <t>First</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Bharuch</t>
+          <t>Second</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kaveripattinam</t>
+          <t>Fourth</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tamralipti</t>
+          <t>Third</t>
         </is>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>The Maurya Empire was established in which century BCE?</t>
+          <t>What was the key feature of Mauryan pillars?</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>7th</t>
+          <t>Red granite</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>6th</t>
+          <t>Sanskrit carvings</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3rd</t>
+          <t>Gold-plated tops</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4th</t>
+          <t>Monolithic and polished</t>
         </is>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
+          <t>Who was Ashoka's chief queen?</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Mahavira</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Sudharma</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Upali</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Bhadrabahu</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>111</v>
+        <v>48</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
+          <t>Who was the head monk at the Third Buddhist Council?</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Ananda</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Kassapa</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Kaniska</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Moggaliputta Tissa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>139</v>
+        <v>56</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
+          <t>Which Mauryan king followed Jainism in his later life?</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
+          <t>Chandragupta Maurya</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>Ashoka</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>Dasharatha</t>
-        </is>
-      </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Which religion did Ashoka promote after the Kalinga War?</t>
+          <t>Who was the mother of Mahendra and Sanghamitra, Ashoka’s children?</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Hinduism</t>
+          <t>Padmavati</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Asandhimitra</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Zoroastrianism</t>
+          <t>Karuvaki</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>149</v>
+        <v>55</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>The Mauryan period marked the beginning of what type of administration?</t>
+          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Democracy</t>
+          <t>Avanti</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Feudalism</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Guild-based</t>
+          <t>Kamboja</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>60</v>
+        <v>130</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Where is the famous rock-cut edict of Ashoka at Dhauli located?</t>
+          <t>Which profession was part of state control under Mauryan rule?</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Weaving</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Teaching</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Medical practice</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Madhya Pradesh</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>37</v>
+        <v>93</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
+          <t>Which Mauryan ruler gave up violence completely?</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Responsible for judiciary</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Minister of religion</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Advisor to Emperor</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Head of treasury</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Which animal represents Ashoka’s Dhamma Chakra?</t>
+          <t>What was the primary language of Ashoka’s southern edicts?</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>What was the primary language of Ashoka’s southern edicts?</t>
+          <t>Who among the following was not sent as a missionary by Ashoka?</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Rakkhita</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Which edict talks about religious tolerance by Ashoka?</t>
+          <t>Who were the Sthanikas in the Mauryan system?</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Village guards</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Minor Rock Edict I</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Pillar Edict III</t>
+          <t>Army commanders</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rock Edict VI</t>
+          <t>Priests</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Major Rock Edict XII</t>
+          <t>Tax collectors</t>
         </is>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>What was the name of the currency used during the Maurya period?</t>
+          <t>Which science was advanced under Mauryan rule?</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Rupya</t>
+          <t>Medicine</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Niska</t>
+          <t>Astronomy</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>Metallurgy</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dinar</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Pana</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>In which language were Ashoka’s inscriptions mostly written?</t>
+          <t>What was the main focus of Ashoka’s Dhamma?</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Military expansion</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Religious conversions</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Moral values and social harmony</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>What was the name of the spy network in Mauryan administration?</t>
+          <t>Which modern Indian state was part of ancient Kalinga?</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Sanstha</t>
+          <t>Bihar</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Chaturanga</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vyayam</t>
+          <t>Assam</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gudhapurusha</t>
+          <t>Odisha</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>117</v>
+        <v>127</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
+          <t>Ashoka's Dhamma was most closely related to which of the following?</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>War strategies</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Territorial expansion</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Moral governance</t>
         </is>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Which Mauryan king was a contemporary of Antiochus II?</t>
+          <t>The Mauryan army was primarily composed of which units?</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Infantry</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Cavalry</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Elephants</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>72</v>
+        <v>126</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>What was the official language of Mauryan administration?</t>
+          <t>Which branch of philosophy did Chanakya support?</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Vedanta</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Samkhya</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>What was the key feature of Mauryan pillars?</t>
+          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Red granite</t>
+          <t>Father</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Sanskrit carvings</t>
+          <t>Uncle</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gold-plated tops</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Monolithic and polished</t>
+          <t>Grandson</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
+          <t>Which ruler was called the "beloved of the gods" in inscriptions?</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Military conquest</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Vedic rituals</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Economic reforms</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Buddhist ethics</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
+          <t>Who succeeded Ashoka as emperor?</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Persian king</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Roman emperor</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Egyptian Pharaoh</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Greek king</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>129</v>
+        <v>104</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
+          <t>Which title did Ashoka use for himself in inscriptions?</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Victory rituals</t>
+          <t>Samrat</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Chakravarti</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Coronation rituals</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Marriage festivals</t>
+          <t>Maharajadhiraja</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Animal sacrifices</t>
+          <t>Devanampiya</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Which profession was supervised during Mauryan times for quality control?</t>
+          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Carpenters</t>
+          <t>Alexander</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Doctors</t>
+          <t>Darius</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Blacksmiths</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>All of these</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>34</v>
+        <v>97</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is located at:</t>
+          <t>The art of polishing stone to a mirror-like finish during Maurya period is called?</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Mauryan glaze</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Ashokan polish</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Mirror carving</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Mauryan polish</t>
         </is>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Which Ashokan edict mentions the Kalinga War?</t>
+          <t>Which ancient traveler gave a detailed account of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Ibn Battuta</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Minor Pillar Edict I</t>
+          <t>Marco Polo</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Pillar Edict VII</t>
+          <t>Fa-Hien</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Major Rock Edict XIII</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>58</v>
+        <v>145</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
+          <t>Which term referred to a municipal officer under the Mauryas?</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Mahamattas</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Nagaraka</t>
         </is>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Which region did Seleucus Nicator give to Chandragupta?</t>
+          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bactria</t>
+          <t>Ashvaghosha</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Armenia</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Syria</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Afghanistan</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Which ancient text is believed to describe the Mauryan administration?</t>
+          <t>What material were most of the Ashokan pillars made from?</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Rigveda</t>
+          <t>Granite</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Sandalwood</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Mahabharata</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ramayana</t>
+          <t>Marble</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Chunar sandstone</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Which modern Indian state was part of ancient Kalinga?</t>
+          <t>Which famous Jain monk influenced Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Mahavira</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Sudharma</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Assam</t>
+          <t>Upali</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bhadrabahu</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112</v>
+        <v>76</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>The Lion Capital of Ashoka is now the emblem of:</t>
+          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Rajatarangini</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>United Nations</t>
+          <t>Indica</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>UNESCO</t>
+          <t>Mahabhashya</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>39</v>
+        <v>73</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Which rock edict talks about Ashoka’s concern for wildlife?</t>
+          <t>Where did Megasthenes reside as a Greek ambassador?</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Kashi</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>12</v>
+        <v>31</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Which Maurya emperor sent missionaries to Sri Lanka?</t>
+          <t>What was the name of the tax collected during the Mauryan rule?</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Bali</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kara</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Sharada</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Bhaga</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>65</v>
+        <v>112</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
+          <t>The Lion Capital of Ashoka is now the emblem of:</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>Buddhism</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Saraswati</t>
+          <t>United Nations</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Yamuna</t>
+          <t>India</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Godavari</t>
+          <t>UNESCO</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ganga</t>
+          <t>India</t>
         </is>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>68</v>
+        <v>147</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>What administrative division existed under Maurya rule?</t>
+          <t>Which officer was responsible for maintaining law and order?</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Janapadas</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Gopa</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Mahajanapadas</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Districts</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Provinces</t>
+          <t>Rajuka</t>
         </is>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Ashoka sent missionaries to which of the following regions?</t>
+          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Egypt</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Arabia</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tibet</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>The Ashokan edicts were mainly meant to:</t>
+          <t>Which Chinese traveler praised the Mauryan governance?</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Promote taxation</t>
+          <t>Xuanzang</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Record wars</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>Praise deities</t>
-        </is>
-      </c>
+          <t>Megasthenes</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Instruct citizens</t>
+          <t>Faxian</t>
         </is>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Which dynasty succeeded the Maurya Empire?</t>
+          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Pliny</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Ptolemy</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kushan</t>
+          <t>Seleucus</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sunga</t>
+          <t>Megasthenes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>35</v>
+        <v>71</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
+          <t>The Mauryas had diplomatic relations with which ancient empire?</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Maharashtra</t>
+          <t>Egyptian</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Karnataka</t>
+          <t>Roman</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Persian</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Greek</t>
         </is>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>13</v>
+        <v>84</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
+          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Brahmi</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Kharosthi</t>
         </is>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>90</v>
+        <v>142</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Who were the "Yonas" mentioned in Ashoka's inscriptions?</t>
+          <t>Who built the first stone Buddhist monuments in India?</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romans</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Persians</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Egyptians</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Greeks</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Which site has a monolithic Ashokan elephant statue?</t>
+          <t>What was the name of the spy network in Mauryan administration?</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Sanstha</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Rampurva</t>
+          <t>Chaturanga</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kumhrar</t>
+          <t>Vyayam</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dhauli</t>
+          <t>Gudhapurusha</t>
         </is>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>92</v>
+        <v>85</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Who was appointed to promote Dhamma among women?</t>
+          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Yuvrajas</t>
+          <t>Rock Edict I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Rock Edict III</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Rajukas</t>
+          <t>Rock Edict XIII</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sanghamitras</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Mahamatras</t>
+          <t>Rock Edict IV</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>What was Ashoka’s relation to Chandragupta Maurya?</t>
+          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Father</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Uncle</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Son</t>
+          <t>Devi</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Rohini</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Grandson</t>
+          <t>Sanghamitra</t>
         </is>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>76</v>
+        <v>146</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Which famous Sanskrit treatise is believed to be written by Chanakya?</t>
+          <t>What was the status of women under Mauryan rule?</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Rajatarangini</t>
+          <t>Highly suppressed</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Indica</t>
+          <t>Equal to men</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Mahabhashya</t>
+          <t>Not mentioned</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Arthashastra</t>
+          <t>Varied by class</t>
         </is>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>86</v>
+        <v>35</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Who was Ashoka's chief queen?</t>
+          <t>Ashoka's inscriptions were discovered in which of these modern states?</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Padmavati</t>
+          <t>Maharashtra</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Karuvaki</t>
+          <t>Karnataka</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>Uttar Pradesh</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Asandhimitra</t>
+          <t>All of the above</t>
         </is>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>82</v>
+        <v>120</v>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Which animal symbolizes loyalty in Ashoka’s pillar carvings?</t>
+          <t>Who is believed to have translated Ashoka’s edicts first in modern history?</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Max Müller</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Alexander Cunningham</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Elephant</t>
+          <t>William Jones</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>James Prinsep</t>
         </is>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>114</v>
+        <v>49</v>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
+          <t>Ashoka’s title "Devanampiya" means:</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Sri Lanka</t>
+          <t>Son of Buddha</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Conqueror of Kalinga</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Narmada</t>
+          <t>Lord of Kings</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Kanyakumari</t>
+          <t>Beloved of the gods</t>
         </is>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>94</v>
+        <v>125</v>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Ashoka’s pillar inscriptions are mainly found in:</t>
+          <t>Which Mauryan emperor ruled the longest?</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Southern India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Western India</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Coastal India</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Northern India</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>29</v>
+        <v>62</v>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Ashoka’s policy after the Kalinga war was called?</t>
+          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Rajadharma</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Ahimsa</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Sangha</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dhamma</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>102</v>
+        <v>149</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Who was the son of Chandragupta Maurya?</t>
+          <t>The Mauryan period marked the beginning of what type of administration?</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Democracy</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Feudalism</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Guild-based</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Centralized bureaucracy</t>
         </is>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Which area was not fully controlled by the Mauryas?</t>
+          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Deccan</t>
+          <t>Shunga</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Satavahana</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kashmir</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tamil Nadu</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>46</v>
+        <v>10</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Which council did Ashoka organize to settle Buddhist disputes?</t>
+          <t>Which of the following was NOT a Mauryan ruler?</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>First Council</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Second Council</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Fourth Council</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Third Council</t>
+          <t>Ajatashatru</t>
         </is>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>69</v>
+        <v>129</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>How many provinces were there during Ashoka’s reign?</t>
+          <t>Ashoka abolished what type of ceremonies after the Kalinga War?</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Victory rituals</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Coronation rituals</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>Marriage festivals</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Animal sacrifices</t>
         </is>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>63</v>
+        <v>100</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Ashoka's inscriptions are found in how many countries outside India?</t>
+          <t>What happened to the Maurya Empire after Ashoka’s death?</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>Expanded</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Became a republic</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>Shifted capital</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>Collapsed quickly</t>
         </is>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Which system did Mauryans follow for currency?</t>
+          <t>Which king was known as “Ashoka the Great”?</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Cowry-based</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Gold coins</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Silver coins</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Punch-marked coins</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>What was the name of Ashoka’s daughter who spread Buddhism in Sri Lanka?</t>
+          <t>Which river did Chandragupta Maurya use to reach Patliputra?</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Devi</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Rohini</t>
+          <t>Son</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Which southern kingdom did Ashoka not conquer?</t>
+          <t>Which Mauryan ruler was known for religious tolerance?</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Pandya</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Chera</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Chola</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>49</v>
+        <v>15</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Ashoka’s title "Devanampiya" means:</t>
+          <t>What was the profession of Chanakya before becoming a political advisor?</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Son of Buddha</t>
+          <t>Poet</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Conqueror of Kalinga</t>
+          <t>Trader</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lord of Kings</t>
+          <t>Monk</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Beloved of the gods</t>
+          <t>Teacher</t>
         </is>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>125</v>
+        <v>54</v>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Which Mauryan emperor ruled the longest?</t>
+          <t>The Maurya Empire was established in which century BCE?</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>7th</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>6th</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>3rd</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>4th</t>
         </is>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Which region did Chandragupta Maurya conquer from the Nandas?</t>
+          <t>What administrative division existed under Maurya rule?</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Avanti</t>
+          <t>Janapadas</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Kalinga</t>
+          <t>Mahajanapadas</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Kamboja</t>
+          <t>Districts</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Provinces</t>
         </is>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>121</v>
+        <v>26</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>The Kalinga war took place around which year?</t>
+          <t>Which southern kingdom did Ashoka not conquer?</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>321 BCE</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>185 BCE</t>
+          <t>Pandya</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>100 BCE</t>
+          <t>Chera</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>261 BCE</t>
+          <t>Chola</t>
         </is>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Where did Chandragupta Maurya spend his last years?</t>
+          <t>In which language were Ashoka’s inscriptions mostly written?</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Nalanda</t>
+          <t>Sanskrit</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Pali</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Tamil</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Shravanabelagola</t>
+          <t>Prakrit</t>
         </is>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>85</v>
+        <v>6</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Which edict mentions Ashoka’s message to forest dwellers?</t>
+          <t>Who succeeded Chandragupta Maurya?</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Rock Edict I</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Rock Edict III</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122</v>
+        <v>79</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Which king was known as “Ashoka the Great”?</t>
+          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
+          <t>Bindusara</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
           <t>Ashoka</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>Bindusara</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>Chandragupta</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4540,917 +4536,921 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>104</v>
+        <v>148</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Which title did Ashoka use for himself in inscriptions?</t>
+          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Samrat</t>
+          <t>Police</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Chakravarti</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Ambassadors</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Maharajadhiraja</t>
+          <t>NGOs</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Civil Services</t>
         </is>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>132</v>
+        <v>116</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Which edict of Ashoka speaks about the welfare of prisoners?</t>
+          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>Horse</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Rock Edict IV</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Minor Rock Edict</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Pillar Edict IV</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Who was the founder of the Maurya Empire?</t>
+          <t>What was the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Chandragupta Maurya</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Which Chinese traveler praised the Mauryan governance?</t>
+          <t>Which Ashokan edict mentions the Kalinga War?</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Xuanzang</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Minor Pillar Edict I</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr"/>
+          <t>Rock Edict I</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Pillar Edict VII</t>
+        </is>
+      </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Faxian</t>
+          <t>Major Rock Edict XIII</t>
         </is>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>107</v>
+        <v>29</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Which language was used in the Ashokan edicts in the eastern regions?</t>
+          <t>Ashoka’s policy after the Kalinga war was called?</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Prakrit</t>
+          <t>Rajadharma</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Pali</t>
+          <t>Ahimsa</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Sangha</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Magadhi</t>
+          <t>Dhamma</t>
         </is>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>41</v>
+        <v>67</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Which city did Ashoka develop into a major Buddhist center?</t>
+          <t>Which of the following was a major port during Mauryan rule?</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Lumbini</t>
+          <t>Lothal</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Bodh Gaya</t>
+          <t>Bharuch</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Kushinagar</t>
+          <t>Kaveripattinam</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sanchi</t>
+          <t>Tamralipti</t>
         </is>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>80</v>
+        <v>135</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Who is believed to have guided Chandragupta Maurya's early political strategies?</t>
+          <t>Which territory was annexed by Ashoka that led to widespread death and regret?</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ashvaghosha</t>
+          <t>Magadha</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Panini</t>
+          <t>Taxila</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Patanjali</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Chanakya</t>
+          <t>Kalinga</t>
         </is>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>The Sanchi Stupa was originally commissioned by:</t>
+          <t>What does the name "Ashoka" literally mean?</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Without enemies</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>One who shines</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Protector of Dharma</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Without sorrow</t>
         </is>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>What does the name "Ashoka" literally mean?</t>
+          <t>Who was the chief minister (Amatya) in Mauryan governance?</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Without enemies</t>
+          <t>Responsible for judiciary</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>One who shines</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Minister of religion</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Protector of Dharma</t>
+          <t>Advisor to Emperor</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Without sorrow</t>
+          <t>Head of treasury</t>
         </is>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>84</v>
+        <v>144</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>The rock edicts of Ashoka are written in which script in the northwest?</t>
+          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Brahmi</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Tamil</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Sanskrit</t>
+          <t>Samprati</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Kharosthi</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>142</v>
+        <v>87</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Who built the first stone Buddhist monuments in India?</t>
+          <t>Which profession was supervised during Mauryan times for quality control?</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Carpenters</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Doctors</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Blacksmiths</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Harsha</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>All of these</t>
         </is>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>137</v>
+        <v>2</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Who compiled the Arthashastra?</t>
+          <t>Which famous teacher and advisor helped Chandragupta Maurya rise to power?</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Patanjali</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Panini</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Bimbisara</t>
+          <t>Vishnu Gupta</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Kautilya</t>
+          <t>Chanakya</t>
         </is>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>31</v>
+        <v>65</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>What was the name of the tax collected during the Mauryan rule?</t>
+          <t>Which river is mentioned frequently in Ashokan inscriptions?</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Bali</t>
+          <t>Saraswati</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Kara</t>
+          <t>Yamuna</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Sharada</t>
+          <t>Godavari</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Bhaga</t>
+          <t>Ganga</t>
         </is>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Which Mauryan king's reign is considered the cultural high point of the dynasty?</t>
+          <t>Which edict talks about religious tolerance by Ashoka?</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Minor Rock Edict I</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Pillar Edict III</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Rock Edict VI</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Major Rock Edict XII</t>
         </is>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>30</v>
+        <v>137</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Which of the following was a key feature of Mauryan administration?</t>
+          <t>Who compiled the Arthashastra?</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Feudal system</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Tribal governance</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Decentralized rule</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Centralized bureaucracy</t>
+          <t>Kautilya</t>
         </is>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>16</v>
+        <v>75</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
+          <t>The Lion Capital of Ashoka has how many lions?</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Allahabad</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Mehrauli</t>
+          <t>4</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Delhi-Topra</t>
+          <t>5</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>4</t>
         </is>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>18</v>
+        <v>38</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Who among the following was not sent as a missionary by Ashoka?</t>
+          <t>The term 'Samaharta' in Mauryan administration meant:</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Mahendra</t>
+          <t>Army general</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Sanghamitra</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Spiritual leader</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Rakkhita</t>
+          <t>Judge</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Devanampiya</t>
+          <t>Tax collector</t>
         </is>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>47</v>
+        <v>105</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Where was the Third Buddhist Council held?</t>
+          <t>Ashoka’s inscriptions refer to which king as Antiochus?</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Rajgir</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Vaishali</t>
+          <t>Persian king</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Roman emperor</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Sarnath</t>
+          <t>Egyptian Pharaoh</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Greek king</t>
         </is>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Which Greek ambassador visited Chandragupta Maurya’s court?</t>
+          <t>Where did Chandragupta Maurya spend his last years?</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Nalanda</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Pliny</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Seleucus</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Megasthenes</t>
+          <t>Shravanabelagola</t>
         </is>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>130</v>
+        <v>101</v>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Which profession was part of state control under Mauryan rule?</t>
+          <t>Which city served as the capital of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Weaving</t>
+          <t>Varanasi</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Teaching</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Medical practice</t>
+          <t>Ujjain</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Rajgir</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Patliputra</t>
         </is>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>138</v>
+        <v>1</v>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>The Ashokan inscription at Girnar is in which modern state?</t>
+          <t>Who was the founder of the Maurya Empire?</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Uttar Pradesh</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Bihar</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Odisha</t>
+          <t>Bimbisara</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Gujarat</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>After which war did Ashoka convert to Buddhism?</t>
+          <t>Who was the Mauryan ruler when Seleucus I invaded India?</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Taxila Revolt</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Battle of Hydaspes</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Battle of Magadha</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Kalinga War</t>
+          <t>Chandragupta Maurya</t>
         </is>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>27</v>
+        <v>88</v>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler is associated with the spread of Buddhism outside India?</t>
+          <t>What was the rank of a provincial governor in Mauryan administration?</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Yuvraja</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Amatya</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dasharatha</t>
+          <t>Mahamatra</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Kumara</t>
         </is>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>145</v>
+        <v>16</v>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Which term referred to a municipal officer under the Mauryas?</t>
+          <t>Which pillar inscription contains Ashoka’s message of Dhamma?</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Gopa</t>
+          <t>Allahabad</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Rajuka</t>
+          <t>Mehrauli</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Mahamattas</t>
+          <t>Delhi-Topra</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Nagaraka</t>
+          <t>Sarnath</t>
         </is>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Which modern institution resembles Ashoka’s Dhamma Mahamattas?</t>
+          <t>What was the main source of revenue in Mauryan administration?</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Police</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Ambassadors</t>
+          <t>Trade</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>NGOs</t>
+          <t>Donations</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Civil Services</t>
+          <t>Agriculture</t>
         </is>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Which Mauryan ruler was known as Devanampiya Piyadasi?</t>
+          <t>Which Mauryan ruler appointed Dhamma Mahamattas?</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
+          <t>Chandragupta</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
           <t>Bindusara</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>Chandragupta</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5472,396 +5472,396 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>103</v>
+        <v>20</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Which dynasty did the Maurya Empire replace in Magadha?</t>
+          <t>Which foreign power signed a treaty with Chandragupta Maurya after war?</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Shunga</t>
+          <t>Egypt</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Rome</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Satavahana</t>
+          <t>China</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Gupta</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Nanda</t>
+          <t>Seleucus Nicator</t>
         </is>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>What significant change did Ashoka make to military policy after Kalinga?</t>
+          <t>Which son of Ashoka ruled the western part of the empire?</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Expansion of navy</t>
+          <t>Kunala</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Increase in cavalry</t>
+          <t>Mahendra</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Recruitment from Kalinga</t>
+          <t>Sumana</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Shift to non-violence</t>
+          <t>Tivala</t>
         </is>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Which Ashokan edict emphasizes the welfare of animals and humans?</t>
+          <t>How many provinces were there during Ashoka’s reign?</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Rock Edict II</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Rock Edict XIII</t>
+          <t>5</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Minor Edict I</t>
+          <t>6</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Rock Edict V</t>
+          <t>5</t>
         </is>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>116</v>
+        <v>33</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Which of the following animals was **NOT** on Ashoka’s Lion Capital?</t>
+          <t>Which ancient text is believed to describe the Mauryan administration?</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Horse</t>
+          <t>Rigveda</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Bull</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Lion</t>
+          <t>Mahabharata</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Ramayana</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Tiger</t>
+          <t>Arthashastra</t>
         </is>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Which natural element was used to polish Mauryan pillars?</t>
+          <t>What was Ashoka’s religion before converting to Buddhism?</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Sand</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Clay</t>
+          <t>Animism</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Quartz</t>
+          <t>Jainism</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Ajivika</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Animal fat</t>
+          <t>Hinduism</t>
         </is>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>What was the profession of Chanakya before becoming a political advisor?</t>
+          <t>The Mauryan Empire extended from Afghanistan to which southern boundary?</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Poet</t>
+          <t>Sri Lanka</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Trader</t>
+          <t>Tamil Nadu</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Monk</t>
+          <t>Narmada</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Teacher</t>
+          <t>Kanyakumari</t>
         </is>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Who was the Greek ruler defeated by Chandragupta Maurya?</t>
+          <t>Which dynasty succeeded the Maurya Empire?</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Alexander</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Darius</t>
+          <t>Gupta</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Nanda</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Ptolemy</t>
+          <t>Kushan</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Seleucus Nicator</t>
+          <t>Sunga</t>
         </is>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Which branch of philosophy did Chanakya support?</t>
+          <t>Who succeeded Chandragupta Maurya after his abdication?</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Buddhism</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Jainism</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Vedanta</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Kaniska</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Samkhya</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>140</v>
+        <v>21</v>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>The Mauryan army was primarily composed of which units?</t>
+          <t>Which animal is prominently featured on the Ashokan Lion Capital?</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Infantry</t>
+          <t>Elephant</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Cavalry</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Elephants</t>
+          <t>Bull</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Tiger</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>All of the above</t>
+          <t>Lion</t>
         </is>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>3</v>
+        <v>110</v>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>What was the capital of the Maurya Empire?</t>
+          <t>The Sanchi Stupa was originally commissioned by:</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Ujjain</t>
+          <t>Chandragupta</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Taxila</t>
+          <t>Bindusara</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Magadha</t>
+          <t>Dasharatha</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Patliputra</t>
+          <t>Ashoka</t>
         </is>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>62</v>
+        <v>77</v>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Which ruler of the Maurya dynasty is considered the greatest?</t>
+          <t>Ashoka’s policy of Dhamma was inspired primarily by which values?</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Bindusara</t>
+          <t>Military conquest</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Chandragupta</t>
+          <t>Vedic rituals</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Samprati</t>
+          <t>Economic reforms</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Ashoka</t>
+          <t>Buddhist ethics</t>
         </is>
       </c>
       <c r="H151" t="inlineStr"/>
